--- a/Zinc/6. Statistical data analysis/Plots by typology/Zn_species_relative_proportions.xlsx
+++ b/Zinc/6. Statistical data analysis/Plots by typology/Zn_species_relative_proportions.xlsx
@@ -1,67 +1,91 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ornl-my.sharepoint.com/personal/q4q_ornl_gov/Documents/Research/Bioavailability Project/BLM_spatial_assessmt/Zinc/6. Statistical data analysis/Plots by typology/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_C2CE303C0001AAD71AB9721D1E0A53129275BF25" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2464FFCC-60D9-4BB0-A131-C64625290837}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
-    <t xml:space="preserve">Typology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free_Zn_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOrg_Zn_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZnCO3_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZnCl_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZnHCO3_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZnOH_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZnSO4_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZnS_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zn_OH_2_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NP Tribs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P Tribs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PD Tribs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main Stem</t>
+    <t>Typology</t>
+  </si>
+  <si>
+    <t>Free_Zn_nM</t>
+  </si>
+  <si>
+    <t>TOrg_Zn_nM</t>
+  </si>
+  <si>
+    <t>ZnCO3_nM</t>
+  </si>
+  <si>
+    <t>ZnCl_nM</t>
+  </si>
+  <si>
+    <t>ZnHCO3_nM</t>
+  </si>
+  <si>
+    <t>ZnOH_nM</t>
+  </si>
+  <si>
+    <t>ZnSO4_nM</t>
+  </si>
+  <si>
+    <t>ZnS_nM</t>
+  </si>
+  <si>
+    <t>Zn_OH_2_nM</t>
+  </si>
+  <si>
+    <t>NP Tribs</t>
+  </si>
+  <si>
+    <t>P Tribs</t>
+  </si>
+  <si>
+    <t>PD Tribs</t>
+  </si>
+  <si>
+    <t>Main Stem</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
+  </numFmts>
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -90,14 +114,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -378,11 +417,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="3" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="11" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -414,136 +459,148 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" t="n">
-        <v>31.3445629192892</v>
-      </c>
-      <c r="C2" t="n">
+      <c r="B2" s="1">
+        <v>31.344562919289199</v>
+      </c>
+      <c r="C2" s="1">
         <v>62.9856829320671</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.575925520969033</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.00533417666685432</v>
-      </c>
-      <c r="F2" t="n">
-        <v>4.47985820432753</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.29562580818551</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.210530942125546</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.000000125357608398277</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.102479371011554</v>
+      <c r="D2" s="1">
+        <v>0.57592552096903304</v>
+      </c>
+      <c r="E2" s="2">
+        <v>5.3341766668543204E-3</v>
+      </c>
+      <c r="F2" s="1">
+        <v>4.4798582043275301</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.29562580818550999</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.21053094212554599</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.2535760839827699E-7</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0.10247937101155399</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" t="n">
-        <v>22.4178114807165</v>
-      </c>
-      <c r="C3" t="n">
-        <v>57.8072090057659</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2.93115706126713</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.00434362526806652</v>
-      </c>
-      <c r="F3" t="n">
-        <v>16.0406367934059</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.437444938797751</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.176585772133446</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.000000406888662777332</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.184810915756653</v>
+      <c r="B3" s="1">
+        <v>22.417811480716502</v>
+      </c>
+      <c r="C3" s="1">
+        <v>57.807209005765898</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2.9311570612671298</v>
+      </c>
+      <c r="E3" s="2">
+        <v>4.3436252680665198E-3</v>
+      </c>
+      <c r="F3" s="1">
+        <v>16.040636793405898</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.43744493879775098</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0.17658577213344601</v>
+      </c>
+      <c r="I3" s="1">
+        <v>4.0688866277733201E-7</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0.18481091575665301</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="n">
-        <v>32.8093501963204</v>
-      </c>
-      <c r="C4" t="n">
-        <v>26.9828607609279</v>
-      </c>
-      <c r="D4" t="n">
-        <v>5.29686418814776</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.0165997023443364</v>
-      </c>
-      <c r="F4" t="n">
-        <v>33.9529423671132</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.537389156505156</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="B4" s="1">
+        <v>32.809350196320402</v>
+      </c>
+      <c r="C4" s="1">
+        <v>26.982860760927899</v>
+      </c>
+      <c r="D4" s="1">
+        <v>5.2968641881477598</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1.6599702344336401E-2</v>
+      </c>
+      <c r="F4" s="1">
+        <v>33.952942367113202</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.53738915650515595</v>
+      </c>
+      <c r="H4" s="1">
         <v>0.193104894834872</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.000000137340620426852</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="I4" s="1">
+        <v>1.3734062042685199E-7</v>
+      </c>
+      <c r="J4" s="1">
         <v>0.210888596465727</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="n">
-        <v>15.9002135613722</v>
-      </c>
-      <c r="C5" t="n">
-        <v>59.3747426013477</v>
-      </c>
-      <c r="D5" t="n">
-        <v>6.00899928955647</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.0140393271749304</v>
-      </c>
-      <c r="F5" t="n">
-        <v>16.2005983249755</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.667881301500676</v>
-      </c>
-      <c r="H5" t="n">
+      <c r="B5" s="1">
+        <v>15.900213561372199</v>
+      </c>
+      <c r="C5" s="1">
+        <v>59.374742601347698</v>
+      </c>
+      <c r="D5" s="1">
+        <v>6.0089992895564697</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1.4039327174930401E-2</v>
+      </c>
+      <c r="F5" s="1">
+        <v>16.200598324975498</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.66788130150067604</v>
+      </c>
+      <c r="H5" s="1">
         <v>0.362409140510145</v>
       </c>
-      <c r="I5" t="n">
-        <v>0.0000000912395569943206</v>
-      </c>
-      <c r="J5" t="n">
+      <c r="I5" s="1">
+        <v>9.1239556994320601E-8</v>
+      </c>
+      <c r="J5" s="1">
         <v>1.47111636232291</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:J5">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/Zinc/6. Statistical data analysis/Plots by typology/Zn_species_relative_proportions.xlsx
+++ b/Zinc/6. Statistical data analysis/Plots by typology/Zn_species_relative_proportions.xlsx
@@ -1,91 +1,70 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ornl-my.sharepoint.com/personal/q4q_ornl_gov/Documents/Research/Bioavailability Project/BLM_spatial_assessmt/Zinc/6. Statistical data analysis/Plots by typology/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_C2CE303C0001AAD71AB9721D1E0A53129275BF25" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2464FFCC-60D9-4BB0-A131-C64625290837}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t>Typology</t>
-  </si>
-  <si>
-    <t>Free_Zn_nM</t>
-  </si>
-  <si>
-    <t>TOrg_Zn_nM</t>
-  </si>
-  <si>
-    <t>ZnCO3_nM</t>
-  </si>
-  <si>
-    <t>ZnCl_nM</t>
-  </si>
-  <si>
-    <t>ZnHCO3_nM</t>
-  </si>
-  <si>
-    <t>ZnOH_nM</t>
-  </si>
-  <si>
-    <t>ZnSO4_nM</t>
-  </si>
-  <si>
-    <t>ZnS_nM</t>
-  </si>
-  <si>
-    <t>Zn_OH_2_nM</t>
-  </si>
-  <si>
-    <t>NP Tribs</t>
-  </si>
-  <si>
-    <t>P Tribs</t>
-  </si>
-  <si>
-    <t>PD Tribs</t>
-  </si>
-  <si>
-    <t>Main Stem</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+  <si>
+    <t xml:space="preserve">Typology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free_Zn_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOrg_Zn_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZnCO3_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZnCl_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZnHCO3_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZnOH_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZnSO4_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZnS_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zn_OH_2_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pooled Water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-Perennial Tribs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perennial Tribs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developed Tribs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main Stem</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="165" formatCode="0.00000"/>
-  </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -114,29 +93,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -417,17 +381,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="3" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="11" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -459,148 +417,168 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="1">
-        <v>31.344562919289199</v>
-      </c>
-      <c r="C2" s="1">
-        <v>62.9856829320671</v>
-      </c>
-      <c r="D2" s="1">
-        <v>0.57592552096903304</v>
-      </c>
-      <c r="E2" s="2">
-        <v>5.3341766668543204E-3</v>
-      </c>
-      <c r="F2" s="1">
-        <v>4.4798582043275301</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.29562580818550999</v>
-      </c>
-      <c r="H2" s="1">
-        <v>0.21053094212554599</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.2535760839827699E-7</v>
-      </c>
-      <c r="J2" s="1">
-        <v>0.10247937101155399</v>
+      <c r="B2" t="n">
+        <v>28.2623133728451</v>
+      </c>
+      <c r="C2" t="n">
+        <v>44.461361578131</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.36364898916267</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0199385690652368</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.5157106253418</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.150111572044596</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.200428646016016</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.000000123203332148403</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0264865241902192</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="1">
-        <v>22.417811480716502</v>
-      </c>
-      <c r="C3" s="1">
-        <v>57.807209005765898</v>
-      </c>
-      <c r="D3" s="1">
-        <v>2.9311570612671298</v>
-      </c>
-      <c r="E3" s="2">
-        <v>4.3436252680665198E-3</v>
-      </c>
-      <c r="F3" s="1">
-        <v>16.040636793405898</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0.43744493879775098</v>
-      </c>
-      <c r="H3" s="1">
-        <v>0.17658577213344601</v>
-      </c>
-      <c r="I3" s="1">
-        <v>4.0688866277733201E-7</v>
-      </c>
-      <c r="J3" s="1">
-        <v>0.18481091575665301</v>
+      <c r="B3" t="n">
+        <v>31.3445629192892</v>
+      </c>
+      <c r="C3" t="n">
+        <v>62.9856829320671</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.575925520969033</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.00533417666685432</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4.47985820432753</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.29562580818551</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.210530942125546</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.000000125357608398277</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.102479371011554</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="1">
-        <v>32.809350196320402</v>
-      </c>
-      <c r="C4" s="1">
-        <v>26.982860760927899</v>
-      </c>
-      <c r="D4" s="1">
-        <v>5.2968641881477598</v>
-      </c>
-      <c r="E4" s="2">
-        <v>1.6599702344336401E-2</v>
-      </c>
-      <c r="F4" s="1">
-        <v>33.952942367113202</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0.53738915650515595</v>
-      </c>
-      <c r="H4" s="1">
-        <v>0.193104894834872</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1.3734062042685199E-7</v>
-      </c>
-      <c r="J4" s="1">
-        <v>0.210888596465727</v>
+      <c r="B4" t="n">
+        <v>22.4178114807165</v>
+      </c>
+      <c r="C4" t="n">
+        <v>57.8072090057659</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.93115706126713</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.00434362526806652</v>
+      </c>
+      <c r="F4" t="n">
+        <v>16.0406367934059</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.437444938797751</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.176585772133446</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.000000406888662777332</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.184810915756653</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5">
       <c r="A5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="1">
-        <v>15.900213561372199</v>
-      </c>
-      <c r="C5" s="1">
-        <v>59.374742601347698</v>
-      </c>
-      <c r="D5" s="1">
-        <v>6.0089992895564697</v>
-      </c>
-      <c r="E5" s="2">
-        <v>1.4039327174930401E-2</v>
-      </c>
-      <c r="F5" s="1">
-        <v>16.200598324975498</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0.66788130150067604</v>
-      </c>
-      <c r="H5" s="1">
+      <c r="B5" t="n">
+        <v>32.8093501963204</v>
+      </c>
+      <c r="C5" t="n">
+        <v>26.9828607609279</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5.29686418814776</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.0165997023443364</v>
+      </c>
+      <c r="F5" t="n">
+        <v>33.9529423671132</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.537389156505156</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.193104894834872</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.000000137340620426852</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.210888596465727</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="n">
+        <v>15.9002135613722</v>
+      </c>
+      <c r="C6" t="n">
+        <v>59.3747426013477</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.00899928955647</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0140393271749304</v>
+      </c>
+      <c r="F6" t="n">
+        <v>16.2005983249755</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.667881301500676</v>
+      </c>
+      <c r="H6" t="n">
         <v>0.362409140510145</v>
       </c>
-      <c r="I5" s="1">
-        <v>9.1239556994320601E-8</v>
-      </c>
-      <c r="J5" s="1">
+      <c r="I6" t="n">
+        <v>0.0000000912395569943206</v>
+      </c>
+      <c r="J6" t="n">
         <v>1.47111636232291</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:J5">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/Zinc/6. Statistical data analysis/Plots by typology/Zn_species_relative_proportions.xlsx
+++ b/Zinc/6. Statistical data analysis/Plots by typology/Zn_species_relative_proportions.xlsx
@@ -44,16 +44,16 @@
     <t xml:space="preserve">Zn_OH_2_nM</t>
   </si>
   <si>
-    <t xml:space="preserve">Pooled Water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-Perennial Tribs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perennial Tribs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developed Tribs</t>
+    <t xml:space="preserve">Pooled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-Perennial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perennial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developed Perennial</t>
   </si>
   <si>
     <t xml:space="preserve">Main Stem</t>
